--- a/updated schedule.xlsx
+++ b/updated schedule.xlsx
@@ -11,7 +11,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Civil_DH_Rural_Mechanical!$A$5:$K$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Cmp_Ele_ELX_IT_SE_IC!$A$2:$C$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Cmp_Ele_ELX_IT_SE_IC!$A$2:$C$49</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t xml:space="preserve">Semester End Examinations Schedule (Spring Semester-2026)</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t xml:space="preserve">Computer Architecture (New)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cancelled Exam</t>
   </si>
   <si>
     <t xml:space="preserve">Data Structure and Algorithms (New)</t>
@@ -410,7 +413,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +434,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="2"/>
+        <bgColor indexed="2"/>
       </patternFill>
     </fill>
   </fills>
@@ -515,7 +524,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -577,6 +586,21 @@
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="2" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="4" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2655,33 +2679,38 @@
       <c r="C29" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="20" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="30" ht="14">
-      <c r="A30" s="6">
+      <c r="A30" s="22">
         <v>46290</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="23" t="s">
         <v>25</v>
       </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="31" ht="15">
-      <c r="A31" s="18">
+      <c r="A31" s="25">
         <v>46291</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="32" ht="15">
@@ -2689,7 +2718,7 @@
         <v>46292</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>23</v>
@@ -2700,7 +2729,7 @@
         <v>46293</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>26</v>
@@ -2712,7 +2741,7 @@
         <v>46294</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>14</v>
@@ -2734,7 +2763,7 @@
         <v>46296</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>19</v>
@@ -2756,7 +2785,7 @@
         <v>46298</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>26</v>
@@ -2767,7 +2796,7 @@
         <v>46299</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>16</v>
@@ -2783,7 +2812,7 @@
       <c r="C40" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="22" t="s">
+      <c r="E40" s="27" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2792,7 +2821,7 @@
         <v>46301</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>16</v>
@@ -2803,7 +2832,7 @@
         <v>46302</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>23</v>
@@ -2815,43 +2844,68 @@
         <v>46303</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="44" ht="14">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="6">
+        <v>46304</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" ht="14">
+      <c r="A45" s="18">
+        <v>46305</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" ht="14">
+      <c r="A46" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="14"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="13">
-        <v>1</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C45" s="23"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="13">
-        <v>2</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" s="24"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="14"/>
     </row>
     <row r="47">
       <c r="A47" s="13">
+        <v>1</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="28"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13">
+        <v>2</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="29"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13">
         <v>3</v>
       </c>
-      <c r="B47" s="12" t="s">
-        <v>114</v>
+      <c r="B49" s="12" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
